--- a/template/RCD_UPDATED.xlsx
+++ b/template/RCD_UPDATED.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\MAIN-SERVER\LGU_TreasuryReportingSystem_$\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A5CC9F-67DA-49D3-8FDB-96CA6ADD4C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE6FF2A-C4D5-4F15-8592-0FA1728018FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="100_GF" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="48">
   <si>
     <t>Municipality of Zamboanguita</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>Name of Accountable Officer:</t>
-  </si>
-  <si>
-    <t>FLORA MY D. FERRER</t>
   </si>
   <si>
     <t>Ending Balance</t>
@@ -281,7 +278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -903,12 +900,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="259">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1092,6 +1111,48 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1137,52 +1198,43 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1209,13 +1261,16 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1230,100 +1285,316 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1335,87 +1606,6 @@
     <xf numFmtId="166" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="168" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1428,166 +1618,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="168" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1602,25 +1642,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1631,6 +1656,18 @@
     </xf>
     <xf numFmtId="43" fontId="5" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1943,7 +1980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF205A66-D080-41F9-A914-9C1726C49817}">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -1953,93 +1990,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="193"/>
+      <c r="A1" s="204" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="206"/>
     </row>
     <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="195"/>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-      <c r="I2" s="195"/>
-      <c r="J2" s="195"/>
-      <c r="K2" s="195"/>
-      <c r="L2" s="195"/>
-      <c r="M2" s="196"/>
+      <c r="B2" s="208"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="209"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="210" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="198"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="199"/>
+      <c r="B3" s="211"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="211"/>
+      <c r="H3" s="211"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="M3" s="212"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="113" t="s">
+      <c r="A4" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="200"/>
-      <c r="K4" s="200"/>
-      <c r="L4" s="200"/>
-      <c r="M4" s="201"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
+      <c r="M4" s="243"/>
     </row>
     <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="189" t="s">
+      <c r="H5" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="189"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="190"/>
+      <c r="I5" s="202"/>
+      <c r="J5" s="162"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="162"/>
+      <c r="M5" s="203"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
@@ -2048,13 +2085,13 @@
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="178"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="190"/>
+      <c r="J6" s="190"/>
       <c r="K6" s="14"/>
-      <c r="L6" s="178"/>
-      <c r="M6" s="179"/>
+      <c r="L6" s="190"/>
+      <c r="M6" s="236"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15"/>
@@ -2072,665 +2109,723 @@
       <c r="M7" s="18"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="180" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="182"/>
-      <c r="E8" s="182"/>
-      <c r="F8" s="182"/>
-      <c r="G8" s="182"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="182"/>
-      <c r="J8" s="184"/>
-      <c r="K8" s="184"/>
-      <c r="L8" s="184"/>
-      <c r="M8" s="185"/>
+      <c r="A8" s="237" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
+      <c r="D8" s="239"/>
+      <c r="E8" s="239"/>
+      <c r="F8" s="239"/>
+      <c r="G8" s="239"/>
+      <c r="H8" s="239"/>
+      <c r="I8" s="239"/>
+      <c r="J8" s="240"/>
+      <c r="K8" s="240"/>
+      <c r="L8" s="240"/>
+      <c r="M8" s="241"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="164" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="165"/>
-      <c r="C9" s="165"/>
-      <c r="D9" s="183"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="183"/>
-      <c r="J9" s="186"/>
-      <c r="K9" s="186"/>
-      <c r="L9" s="186"/>
-      <c r="M9" s="187"/>
+      <c r="A9" s="173" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="196"/>
+      <c r="E9" s="196"/>
+      <c r="F9" s="196"/>
+      <c r="G9" s="196"/>
+      <c r="H9" s="196"/>
+      <c r="I9" s="196"/>
+      <c r="J9" s="199"/>
+      <c r="K9" s="199"/>
+      <c r="L9" s="199"/>
+      <c r="M9" s="200"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="161" t="s">
+      <c r="A10" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="162"/>
-      <c r="C10" s="163"/>
-      <c r="D10" s="167" t="s">
+      <c r="B10" s="171"/>
+      <c r="C10" s="172"/>
+      <c r="D10" s="176" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="168"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="168"/>
-      <c r="I10" s="169"/>
-      <c r="J10" s="168" t="s">
+      <c r="E10" s="177"/>
+      <c r="F10" s="177"/>
+      <c r="G10" s="177"/>
+      <c r="H10" s="177"/>
+      <c r="I10" s="178"/>
+      <c r="J10" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="168"/>
-      <c r="L10" s="168"/>
-      <c r="M10" s="169"/>
+      <c r="K10" s="177"/>
+      <c r="L10" s="177"/>
+      <c r="M10" s="178"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="164"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="166"/>
-      <c r="D11" s="170"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="79"/>
+      <c r="A11" s="173"/>
+      <c r="B11" s="174"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="179"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
+      <c r="L11" s="92"/>
+      <c r="M11" s="93"/>
     </row>
     <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="148"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="171"/>
-      <c r="E12" s="172"/>
-      <c r="F12" s="173"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="172"/>
-      <c r="I12" s="173"/>
-      <c r="J12" s="174"/>
-      <c r="K12" s="175"/>
-      <c r="L12" s="175"/>
-      <c r="M12" s="176"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="79"/>
     </row>
     <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="131"/>
-      <c r="B13" s="120"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="152"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="154"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="153"/>
-      <c r="I13" s="154"/>
-      <c r="J13" s="155"/>
-      <c r="K13" s="156"/>
-      <c r="L13" s="156"/>
-      <c r="M13" s="157"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="131"/>
-      <c r="B14" s="120"/>
-      <c r="C14" s="120"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="158">
-        <f>SUM(J12:M13)</f>
+      <c r="A13" s="82"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="79"/>
+    </row>
+    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="82"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="79"/>
+    </row>
+    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="82"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="78"/>
+      <c r="M15" s="79"/>
+    </row>
+    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="82"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="79"/>
+    </row>
+    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="142"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="161"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="163"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="163"/>
+      <c r="J17" s="164"/>
+      <c r="K17" s="165"/>
+      <c r="L17" s="165"/>
+      <c r="M17" s="166"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="142"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="167">
+        <f>SUM(J12:M17)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="159"/>
-      <c r="L14" s="159"/>
-      <c r="M14" s="160"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="145" t="s">
+      <c r="K18" s="168"/>
+      <c r="L18" s="168"/>
+      <c r="M18" s="169"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="146"/>
-      <c r="C15" s="146"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="146"/>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="147"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="148" t="s">
+      <c r="B19" s="156"/>
+      <c r="C19" s="156"/>
+      <c r="D19" s="156"/>
+      <c r="E19" s="156"/>
+      <c r="F19" s="156"/>
+      <c r="G19" s="156"/>
+      <c r="H19" s="156"/>
+      <c r="I19" s="156"/>
+      <c r="J19" s="156"/>
+      <c r="K19" s="156"/>
+      <c r="L19" s="156"/>
+      <c r="M19" s="157"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="128"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="127" t="s">
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="128"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="127"/>
-      <c r="K16" s="128"/>
-      <c r="L16" s="128"/>
-      <c r="M16" s="130"/>
-    </row>
-    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="135" t="s">
+      <c r="H20" s="83"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="231"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="232"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="149"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="151"/>
-    </row>
-    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="123"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="124" t="s">
+      <c r="B21" s="147"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="147"/>
+      <c r="F21" s="148"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="233"/>
+      <c r="K21" s="234"/>
+      <c r="L21" s="234"/>
+      <c r="M21" s="235"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="134"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="135"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="136"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="125"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="127" t="s">
+      <c r="B23" s="138"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="139"/>
+      <c r="G23" s="231" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="128"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="127" t="s">
+      <c r="H23" s="83"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="231" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="128"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="130"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="131" t="s">
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="232"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="142" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="120"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="117" t="s">
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="120"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="132"/>
-      <c r="K20" s="133"/>
-      <c r="L20" s="133"/>
-      <c r="M20" s="134"/>
-    </row>
-    <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="135"/>
-      <c r="B21" s="136"/>
-      <c r="C21" s="136"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="136"/>
-      <c r="I21" s="137"/>
-      <c r="J21" s="139"/>
-      <c r="K21" s="140"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="141"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="142" t="s">
+      <c r="H24" s="133"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="144"/>
+      <c r="L24" s="144"/>
+      <c r="M24" s="145"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="146"/>
+      <c r="B25" s="147"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="147"/>
+      <c r="F25" s="148"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="147"/>
+      <c r="I25" s="148"/>
+      <c r="J25" s="150"/>
+      <c r="K25" s="151"/>
+      <c r="L25" s="151"/>
+      <c r="M25" s="152"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="143"/>
-      <c r="C22" s="143"/>
-      <c r="D22" s="143"/>
-      <c r="E22" s="143"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="143"/>
-      <c r="J22" s="125"/>
-      <c r="K22" s="125"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="144"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="119" t="s">
+      <c r="B26" s="154"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="154"/>
+      <c r="I26" s="154"/>
+      <c r="J26" s="138"/>
+      <c r="K26" s="138"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="141"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="230" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="117" t="s">
+      <c r="B27" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="120"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="111" t="s">
+      <c r="C27" s="133"/>
+      <c r="D27" s="129"/>
+      <c r="E27" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111" t="s">
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111" t="s">
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="L23" s="111"/>
-      <c r="M23" s="112"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="119"/>
-      <c r="B24" s="110" t="s">
+      <c r="L27" s="81"/>
+      <c r="M27" s="229"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="230"/>
+      <c r="B28" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="117" t="s">
+      <c r="C28" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="118"/>
-      <c r="E24" s="110" t="s">
+      <c r="D28" s="129"/>
+      <c r="E28" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="117" t="s">
+      <c r="F28" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="118"/>
-      <c r="H24" s="110" t="s">
+      <c r="G28" s="129"/>
+      <c r="H28" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="111" t="s">
+      <c r="I28" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="111"/>
-      <c r="K24" s="110" t="s">
+      <c r="J28" s="81"/>
+      <c r="K28" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="111" t="s">
+      <c r="L28" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="M24" s="112"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="119"/>
-      <c r="B25" s="110"/>
-      <c r="C25" s="20" t="s">
+      <c r="M28" s="229"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="230"/>
+      <c r="B29" s="228"/>
+      <c r="C29" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="110"/>
-      <c r="F25" s="20" t="s">
+      <c r="E29" s="228"/>
+      <c r="F29" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="110"/>
-      <c r="I25" s="20" t="s">
+      <c r="H29" s="228"/>
+      <c r="I29" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="J25" s="20" t="s">
+      <c r="J29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K25" s="110"/>
-      <c r="L25" s="20" t="s">
+      <c r="K29" s="228"/>
+      <c r="L29" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="M25" s="21" t="s">
+      <c r="M29" s="21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="41"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="21"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="41"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="21"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="3"/>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="41"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="21"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="41"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="21"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="25" t="s">
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="J31" s="19"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="27"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="113" t="s">
+      <c r="J35" s="19"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="27"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="125" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="114"/>
-      <c r="C32" s="114"/>
-      <c r="D32" s="114"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="114"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="115"/>
-      <c r="K32" s="115"/>
-      <c r="L32" s="115"/>
-      <c r="M32" s="116"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="113" t="s">
+      <c r="B36" s="126"/>
+      <c r="C36" s="126"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="126"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="127"/>
+      <c r="K36" s="127"/>
+      <c r="L36" s="127"/>
+      <c r="M36" s="128"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="114"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="114"/>
-      <c r="E33" s="114"/>
-      <c r="F33" s="114"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="104">
-        <f>J14</f>
+      <c r="B37" s="126"/>
+      <c r="C37" s="126"/>
+      <c r="D37" s="126"/>
+      <c r="E37" s="126"/>
+      <c r="F37" s="126"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="115">
+        <f>J18</f>
         <v>0</v>
       </c>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="105"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="102" t="s">
+      <c r="K37" s="115"/>
+      <c r="L37" s="115"/>
+      <c r="M37" s="116"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="103"/>
-      <c r="C34" s="103"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="103"/>
-      <c r="F34" s="103"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="104"/>
-      <c r="K34" s="104"/>
-      <c r="L34" s="104"/>
-      <c r="M34" s="105"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="102" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="103"/>
-      <c r="C35" s="103"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="104"/>
-      <c r="K35" s="104"/>
-      <c r="L35" s="104"/>
-      <c r="M35" s="105"/>
-    </row>
-    <row r="36" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="106" t="s">
+      <c r="B38" s="114"/>
+      <c r="C38" s="114"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="114"/>
+      <c r="F38" s="114"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="115"/>
+      <c r="K38" s="115"/>
+      <c r="L38" s="115"/>
+      <c r="M38" s="116"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="113" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="114"/>
+      <c r="C39" s="114"/>
+      <c r="D39" s="114"/>
+      <c r="E39" s="114"/>
+      <c r="F39" s="114"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="115"/>
+      <c r="K39" s="115"/>
+      <c r="L39" s="115"/>
+      <c r="M39" s="116"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="107"/>
-      <c r="C36" s="107"/>
-      <c r="D36" s="107"/>
-      <c r="E36" s="107"/>
-      <c r="F36" s="107"/>
-      <c r="G36" s="107"/>
-      <c r="H36" s="107"/>
-      <c r="I36" s="107"/>
-      <c r="J36" s="108"/>
-      <c r="K36" s="108"/>
-      <c r="L36" s="108"/>
-      <c r="M36" s="109"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="80" t="s">
+      <c r="B40" s="118"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="119"/>
+      <c r="K40" s="119"/>
+      <c r="L40" s="119"/>
+      <c r="M40" s="120"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="81"/>
-      <c r="C37" s="81"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="80" t="s">
+      <c r="B41" s="95"/>
+      <c r="C41" s="95"/>
+      <c r="D41" s="95"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="H37" s="81"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="81"/>
-      <c r="K37" s="81"/>
-      <c r="L37" s="81"/>
-      <c r="M37" s="82"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="83" t="s">
+      <c r="H41" s="95"/>
+      <c r="I41" s="95"/>
+      <c r="J41" s="95"/>
+      <c r="K41" s="95"/>
+      <c r="L41" s="95"/>
+      <c r="M41" s="96"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="98"/>
+      <c r="C42" s="98"/>
+      <c r="D42" s="98"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="84"/>
-      <c r="C38" s="84"/>
-      <c r="D38" s="84"/>
-      <c r="E38" s="84"/>
-      <c r="F38" s="84"/>
-      <c r="G38" s="83" t="s">
-        <v>46</v>
-      </c>
-      <c r="H38" s="84"/>
-      <c r="I38" s="84"/>
-      <c r="J38" s="84"/>
-      <c r="K38" s="84"/>
-      <c r="L38" s="84"/>
-      <c r="M38" s="85"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
-      <c r="B39" s="84"/>
-      <c r="C39" s="84"/>
-      <c r="D39" s="84"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="84"/>
-      <c r="K39" s="84"/>
-      <c r="L39" s="84"/>
-      <c r="M39" s="85"/>
-    </row>
-    <row r="40" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="83"/>
-      <c r="B40" s="84"/>
-      <c r="C40" s="84"/>
-      <c r="D40" s="84"/>
-      <c r="E40" s="84"/>
-      <c r="F40" s="84"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="84"/>
-      <c r="I40" s="84"/>
-      <c r="J40" s="84"/>
-      <c r="K40" s="84"/>
-      <c r="L40" s="84"/>
-      <c r="M40" s="85"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="86" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="88"/>
-      <c r="E41" s="92">
+      <c r="H42" s="98"/>
+      <c r="I42" s="98"/>
+      <c r="J42" s="98"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="98"/>
+      <c r="M42" s="99"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="97"/>
+      <c r="B43" s="98"/>
+      <c r="C43" s="98"/>
+      <c r="D43" s="98"/>
+      <c r="E43" s="98"/>
+      <c r="F43" s="98"/>
+      <c r="G43" s="97"/>
+      <c r="H43" s="98"/>
+      <c r="I43" s="98"/>
+      <c r="J43" s="98"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="98"/>
+      <c r="M43" s="99"/>
+    </row>
+    <row r="44" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="97"/>
+      <c r="B44" s="98"/>
+      <c r="C44" s="98"/>
+      <c r="D44" s="98"/>
+      <c r="E44" s="98"/>
+      <c r="F44" s="98"/>
+      <c r="G44" s="97"/>
+      <c r="H44" s="98"/>
+      <c r="I44" s="98"/>
+      <c r="J44" s="98"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="99"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="215"/>
+      <c r="B45" s="216"/>
+      <c r="C45" s="216"/>
+      <c r="D45" s="217"/>
+      <c r="E45" s="221">
         <f>J4</f>
         <v>0</v>
       </c>
-      <c r="F41" s="93"/>
-      <c r="G41" s="86" t="s">
-        <v>36</v>
-      </c>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="98">
+      <c r="F45" s="105"/>
+      <c r="G45" s="215" t="s">
+        <v>35</v>
+      </c>
+      <c r="H45" s="216"/>
+      <c r="I45" s="216"/>
+      <c r="J45" s="216"/>
+      <c r="K45" s="222"/>
+      <c r="L45" s="224">
         <f>J4</f>
         <v>0</v>
       </c>
-      <c r="M41" s="99"/>
-    </row>
-    <row r="42" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="89"/>
-      <c r="B42" s="90"/>
-      <c r="C42" s="90"/>
-      <c r="D42" s="91"/>
-      <c r="E42" s="94"/>
-      <c r="F42" s="95"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="90"/>
-      <c r="I42" s="90"/>
-      <c r="J42" s="90"/>
-      <c r="K42" s="97"/>
-      <c r="L42" s="100"/>
-      <c r="M42" s="101"/>
-    </row>
-    <row r="43" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="71" t="s">
+      <c r="M45" s="225"/>
+    </row>
+    <row r="46" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="218"/>
+      <c r="B46" s="219"/>
+      <c r="C46" s="219"/>
+      <c r="D46" s="220"/>
+      <c r="E46" s="107"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="218"/>
+      <c r="H46" s="219"/>
+      <c r="I46" s="219"/>
+      <c r="J46" s="219"/>
+      <c r="K46" s="223"/>
+      <c r="L46" s="226"/>
+      <c r="M46" s="227"/>
+    </row>
+    <row r="47" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="86"/>
+      <c r="C47" s="86"/>
+      <c r="D47" s="87"/>
+      <c r="E47" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="72"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="74" t="s">
+      <c r="F47" s="89"/>
+      <c r="G47" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="F43" s="75"/>
-      <c r="G43" s="76" t="s">
-        <v>39</v>
-      </c>
-      <c r="H43" s="77"/>
-      <c r="I43" s="77"/>
-      <c r="J43" s="77"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="78" t="s">
-        <v>38</v>
-      </c>
-      <c r="M43" s="79"/>
+      <c r="H47" s="91"/>
+      <c r="I47" s="91"/>
+      <c r="J47" s="91"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="92" t="s">
+        <v>37</v>
+      </c>
+      <c r="M47" s="93"/>
     </row>
   </sheetData>
-  <mergeCells count="83">
+  <mergeCells count="99">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="H5:I5"/>
@@ -2754,66 +2849,82 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="J12:M12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="A19:M19"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="J21:M21"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="J36:M36"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="L43:M43"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="G37:M37"/>
-    <mergeCell ref="A38:F40"/>
-    <mergeCell ref="G38:M40"/>
-    <mergeCell ref="A41:D42"/>
-    <mergeCell ref="E41:F42"/>
-    <mergeCell ref="G41:K42"/>
-    <mergeCell ref="L41:M42"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="G41:M41"/>
+    <mergeCell ref="A42:F44"/>
+    <mergeCell ref="G42:M44"/>
+    <mergeCell ref="A45:D46"/>
+    <mergeCell ref="E45:F46"/>
+    <mergeCell ref="G45:K46"/>
+    <mergeCell ref="L45:M46"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2821,7 +2932,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B18D47-C496-4BD2-99BC-DA2F435C6A15}">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
@@ -2829,93 +2940,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="193"/>
+      <c r="A1" s="204" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="206"/>
     </row>
     <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="195"/>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-      <c r="I2" s="195"/>
-      <c r="J2" s="195"/>
-      <c r="K2" s="195"/>
-      <c r="L2" s="195"/>
-      <c r="M2" s="196"/>
+      <c r="B2" s="208"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="209"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="210" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="198"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="199"/>
+      <c r="B3" s="211"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="211"/>
+      <c r="H3" s="211"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="M3" s="212"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="113" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
+      <c r="A4" s="125" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
-      <c r="M4" s="236"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="214"/>
     </row>
     <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="189" t="s">
+      <c r="H5" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="189"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="190"/>
+      <c r="I5" s="202"/>
+      <c r="J5" s="162"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="162"/>
+      <c r="M5" s="203"/>
     </row>
     <row r="6" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
@@ -2924,13 +3035,13 @@
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="178"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="190"/>
+      <c r="J6" s="190"/>
       <c r="K6" s="14"/>
-      <c r="L6" s="228"/>
-      <c r="M6" s="229"/>
+      <c r="L6" s="191"/>
+      <c r="M6" s="192"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15"/>
@@ -2948,635 +3059,738 @@
       <c r="M7" s="18"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="230" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="231"/>
-      <c r="C8" s="231"/>
-      <c r="D8" s="232"/>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-      <c r="G8" s="232"/>
-      <c r="H8" s="232"/>
-      <c r="I8" s="232"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="234"/>
+      <c r="A8" s="193" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="195"/>
+      <c r="E8" s="195"/>
+      <c r="F8" s="195"/>
+      <c r="G8" s="195"/>
+      <c r="H8" s="195"/>
+      <c r="I8" s="195"/>
+      <c r="J8" s="197"/>
+      <c r="K8" s="197"/>
+      <c r="L8" s="197"/>
+      <c r="M8" s="198"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="164" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="165"/>
-      <c r="C9" s="165"/>
-      <c r="D9" s="183"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="183"/>
-      <c r="J9" s="186"/>
-      <c r="K9" s="186"/>
-      <c r="L9" s="186"/>
-      <c r="M9" s="187"/>
+      <c r="A9" s="173" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="196"/>
+      <c r="E9" s="196"/>
+      <c r="F9" s="196"/>
+      <c r="G9" s="196"/>
+      <c r="H9" s="196"/>
+      <c r="I9" s="196"/>
+      <c r="J9" s="199"/>
+      <c r="K9" s="199"/>
+      <c r="L9" s="199"/>
+      <c r="M9" s="200"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="161" t="s">
+      <c r="A10" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="162"/>
-      <c r="C10" s="163"/>
-      <c r="D10" s="167" t="s">
+      <c r="B10" s="171"/>
+      <c r="C10" s="172"/>
+      <c r="D10" s="176" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="168"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="168"/>
-      <c r="I10" s="169"/>
-      <c r="J10" s="167" t="s">
+      <c r="E10" s="177"/>
+      <c r="F10" s="177"/>
+      <c r="G10" s="177"/>
+      <c r="H10" s="177"/>
+      <c r="I10" s="178"/>
+      <c r="J10" s="176" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="168"/>
-      <c r="L10" s="168"/>
-      <c r="M10" s="169"/>
+      <c r="K10" s="177"/>
+      <c r="L10" s="177"/>
+      <c r="M10" s="178"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="164"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="166"/>
-      <c r="D11" s="170"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="170"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="79"/>
+      <c r="A11" s="173"/>
+      <c r="B11" s="174"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="179"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="179"/>
+      <c r="K11" s="92"/>
+      <c r="L11" s="92"/>
+      <c r="M11" s="93"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="124"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="222"/>
-      <c r="E12" s="223"/>
-      <c r="F12" s="224"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="223"/>
-      <c r="I12" s="224"/>
-      <c r="J12" s="225"/>
-      <c r="K12" s="226"/>
-      <c r="L12" s="226"/>
-      <c r="M12" s="227"/>
-    </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="131"/>
-      <c r="B13" s="120"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="152"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="154"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="153"/>
-      <c r="I13" s="154"/>
-      <c r="J13" s="155"/>
-      <c r="K13" s="156"/>
-      <c r="L13" s="156"/>
-      <c r="M13" s="157"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="131"/>
-      <c r="B14" s="120"/>
-      <c r="C14" s="120"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="158">
-        <f>SUM(J12:M13)</f>
+      <c r="A12" s="180"/>
+      <c r="B12" s="181"/>
+      <c r="C12" s="182"/>
+      <c r="D12" s="183"/>
+      <c r="E12" s="184"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="183"/>
+      <c r="H12" s="184"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="187"/>
+      <c r="L12" s="187"/>
+      <c r="M12" s="188"/>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="80"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="76"/>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="80"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="75"/>
+      <c r="M14" s="76"/>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="80"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="76"/>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="82"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="79"/>
+    </row>
+    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="142"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="161"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="163"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="163"/>
+      <c r="J17" s="164"/>
+      <c r="K17" s="165"/>
+      <c r="L17" s="165"/>
+      <c r="M17" s="166"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="142"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="167">
+        <f>SUM(J12:M17)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="159"/>
-      <c r="L14" s="159"/>
-      <c r="M14" s="160"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="145" t="s">
+      <c r="K18" s="168"/>
+      <c r="L18" s="168"/>
+      <c r="M18" s="169"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="146"/>
-      <c r="C15" s="146"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="146"/>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="147"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="131" t="s">
+      <c r="B19" s="156"/>
+      <c r="C19" s="156"/>
+      <c r="D19" s="156"/>
+      <c r="E19" s="156"/>
+      <c r="F19" s="156"/>
+      <c r="G19" s="156"/>
+      <c r="H19" s="156"/>
+      <c r="I19" s="156"/>
+      <c r="J19" s="156"/>
+      <c r="K19" s="156"/>
+      <c r="L19" s="156"/>
+      <c r="M19" s="157"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="117" t="s">
+      <c r="B20" s="133"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="120"/>
-      <c r="I16" s="118"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="214"/>
-    </row>
-    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="135" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="137"/>
-      <c r="J17" s="219"/>
-      <c r="K17" s="220"/>
-      <c r="L17" s="220"/>
-      <c r="M17" s="221"/>
-    </row>
-    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="123"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="124" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="125"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="218" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="125"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="218" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="125"/>
-      <c r="L19" s="125"/>
-      <c r="M19" s="144"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="131" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="120"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="117" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="120"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="132"/>
+      <c r="H20" s="133"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="123"/>
       <c r="K20" s="133"/>
       <c r="L20" s="133"/>
-      <c r="M20" s="134"/>
+      <c r="M20" s="124"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="135"/>
-      <c r="B21" s="136"/>
-      <c r="C21" s="136"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="136"/>
-      <c r="I21" s="137"/>
-      <c r="J21" s="139"/>
-      <c r="K21" s="140"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="141"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="142" t="s">
+      <c r="A21" s="146" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="147"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="147"/>
+      <c r="F21" s="148"/>
+      <c r="G21" s="149"/>
+      <c r="H21" s="147"/>
+      <c r="I21" s="148"/>
+      <c r="J21" s="158"/>
+      <c r="K21" s="159"/>
+      <c r="L21" s="159"/>
+      <c r="M21" s="160"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="134"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="135"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="136"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="137" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="138"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="139"/>
+      <c r="G23" s="140" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="138"/>
+      <c r="I23" s="139"/>
+      <c r="J23" s="140" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="138"/>
+      <c r="L23" s="138"/>
+      <c r="M23" s="141"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="142" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="123" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="133"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="144"/>
+      <c r="L24" s="144"/>
+      <c r="M24" s="145"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="146"/>
+      <c r="B25" s="147"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="147"/>
+      <c r="F25" s="148"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="147"/>
+      <c r="I25" s="148"/>
+      <c r="J25" s="150"/>
+      <c r="K25" s="151"/>
+      <c r="L25" s="151"/>
+      <c r="M25" s="152"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="143"/>
-      <c r="C22" s="143"/>
-      <c r="D22" s="143"/>
-      <c r="E22" s="143"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="143"/>
-      <c r="J22" s="125"/>
-      <c r="K22" s="125"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="144"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="215" t="s">
+      <c r="B26" s="154"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="154"/>
+      <c r="I26" s="154"/>
+      <c r="J26" s="138"/>
+      <c r="K26" s="138"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="141"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="117" t="s">
+      <c r="B27" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="120"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="117" t="s">
+      <c r="C27" s="133"/>
+      <c r="D27" s="129"/>
+      <c r="E27" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="120"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="117" t="s">
+      <c r="F27" s="133"/>
+      <c r="G27" s="129"/>
+      <c r="H27" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="I23" s="120"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="117" t="s">
+      <c r="I27" s="133"/>
+      <c r="J27" s="129"/>
+      <c r="K27" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="L23" s="120"/>
-      <c r="M23" s="214"/>
-    </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="216"/>
-      <c r="B24" s="212" t="s">
+      <c r="L27" s="133"/>
+      <c r="M27" s="124"/>
+    </row>
+    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="131"/>
+      <c r="B28" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="117" t="s">
+      <c r="C28" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="118"/>
-      <c r="E24" s="212" t="s">
+      <c r="D28" s="129"/>
+      <c r="E28" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="117" t="s">
+      <c r="F28" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="118"/>
-      <c r="H24" s="212" t="s">
+      <c r="G28" s="129"/>
+      <c r="H28" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="117" t="s">
+      <c r="I28" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="118"/>
-      <c r="K24" s="212" t="s">
+      <c r="J28" s="129"/>
+      <c r="K28" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="117" t="s">
+      <c r="L28" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="M24" s="214"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
-      <c r="B25" s="213"/>
-      <c r="C25" s="20" t="s">
+      <c r="M28" s="124"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="132"/>
+      <c r="B29" s="122"/>
+      <c r="C29" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="213"/>
-      <c r="F25" s="20" t="s">
+      <c r="E29" s="122"/>
+      <c r="F29" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="213"/>
-      <c r="I25" s="20" t="s">
+      <c r="H29" s="122"/>
+      <c r="I29" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="J25" s="20" t="s">
+      <c r="J29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K25" s="213"/>
-      <c r="L25" s="20" t="s">
+      <c r="K29" s="122"/>
+      <c r="L29" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="M25" s="21" t="s">
+      <c r="M29" s="21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="40"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="21"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="40"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="21"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="40"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="21"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="40"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="21"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="40"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="21"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="25" t="s">
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="J29" s="19"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="27"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="113" t="s">
+      <c r="J36" s="19"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="27"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="125" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="114"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="115"/>
-      <c r="K30" s="115"/>
-      <c r="L30" s="115"/>
-      <c r="M30" s="116"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="113" t="s">
+      <c r="B37" s="126"/>
+      <c r="C37" s="126"/>
+      <c r="D37" s="126"/>
+      <c r="E37" s="126"/>
+      <c r="F37" s="126"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="127"/>
+      <c r="K37" s="127"/>
+      <c r="L37" s="127"/>
+      <c r="M37" s="128"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="114"/>
-      <c r="C31" s="114"/>
-      <c r="D31" s="114"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="114"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="104">
-        <f>J14</f>
+      <c r="B38" s="126"/>
+      <c r="C38" s="126"/>
+      <c r="D38" s="126"/>
+      <c r="E38" s="126"/>
+      <c r="F38" s="126"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="115">
+        <f>J18</f>
         <v>0</v>
       </c>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="105"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="102" t="s">
+      <c r="K38" s="115"/>
+      <c r="L38" s="115"/>
+      <c r="M38" s="116"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="103"/>
-      <c r="C32" s="103"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="103"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="105"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="102" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="103"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="105"/>
-    </row>
-    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="106" t="s">
+      <c r="B39" s="114"/>
+      <c r="C39" s="114"/>
+      <c r="D39" s="114"/>
+      <c r="E39" s="114"/>
+      <c r="F39" s="114"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="115"/>
+      <c r="K39" s="115"/>
+      <c r="L39" s="115"/>
+      <c r="M39" s="116"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="113" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="114"/>
+      <c r="C40" s="114"/>
+      <c r="D40" s="114"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="114"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="115"/>
+      <c r="K40" s="115"/>
+      <c r="L40" s="115"/>
+      <c r="M40" s="116"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="107"/>
-      <c r="C34" s="107"/>
-      <c r="D34" s="107"/>
-      <c r="E34" s="107"/>
-      <c r="F34" s="107"/>
-      <c r="G34" s="107"/>
-      <c r="H34" s="107"/>
-      <c r="I34" s="107"/>
-      <c r="J34" s="108"/>
-      <c r="K34" s="108"/>
-      <c r="L34" s="108"/>
-      <c r="M34" s="109"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="80" t="s">
+      <c r="B41" s="118"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="118"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="119"/>
+      <c r="K41" s="119"/>
+      <c r="L41" s="119"/>
+      <c r="M41" s="120"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="81"/>
-      <c r="C35" s="81"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="82"/>
-      <c r="G35" s="80" t="s">
+      <c r="B42" s="95"/>
+      <c r="C42" s="95"/>
+      <c r="D42" s="95"/>
+      <c r="E42" s="95"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="H35" s="81"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="81"/>
-      <c r="K35" s="81"/>
-      <c r="L35" s="81"/>
-      <c r="M35" s="82"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="83" t="s">
+      <c r="H42" s="95"/>
+      <c r="I42" s="95"/>
+      <c r="J42" s="95"/>
+      <c r="K42" s="95"/>
+      <c r="L42" s="95"/>
+      <c r="M42" s="96"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="98"/>
+      <c r="C43" s="98"/>
+      <c r="D43" s="98"/>
+      <c r="E43" s="98"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="84"/>
-      <c r="C36" s="84"/>
-      <c r="D36" s="84"/>
-      <c r="E36" s="84"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="83" t="s">
-        <v>46</v>
-      </c>
-      <c r="H36" s="84"/>
-      <c r="I36" s="84"/>
-      <c r="J36" s="84"/>
-      <c r="K36" s="84"/>
-      <c r="L36" s="84"/>
-      <c r="M36" s="85"/>
-    </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
-      <c r="B37" s="84"/>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="85"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="84"/>
-      <c r="J37" s="84"/>
-      <c r="K37" s="84"/>
-      <c r="L37" s="84"/>
-      <c r="M37" s="85"/>
-    </row>
-    <row r="38" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="202"/>
-      <c r="B38" s="203"/>
-      <c r="C38" s="203"/>
-      <c r="D38" s="203"/>
-      <c r="E38" s="203"/>
-      <c r="F38" s="204"/>
-      <c r="G38" s="202"/>
-      <c r="H38" s="203"/>
-      <c r="I38" s="203"/>
-      <c r="J38" s="203"/>
-      <c r="K38" s="203"/>
-      <c r="L38" s="203"/>
-      <c r="M38" s="204"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="205" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="206"/>
-      <c r="C39" s="206"/>
-      <c r="D39" s="93"/>
-      <c r="E39" s="208">
+      <c r="H43" s="98"/>
+      <c r="I43" s="98"/>
+      <c r="J43" s="98"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="98"/>
+      <c r="M43" s="99"/>
+    </row>
+    <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="97"/>
+      <c r="B44" s="98"/>
+      <c r="C44" s="98"/>
+      <c r="D44" s="98"/>
+      <c r="E44" s="98"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="97"/>
+      <c r="H44" s="98"/>
+      <c r="I44" s="98"/>
+      <c r="J44" s="98"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="99"/>
+    </row>
+    <row r="45" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="100"/>
+      <c r="B45" s="101"/>
+      <c r="C45" s="101"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="101"/>
+      <c r="F45" s="102"/>
+      <c r="G45" s="100"/>
+      <c r="H45" s="101"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="101"/>
+      <c r="M45" s="102"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="103"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="109">
         <f>J4</f>
         <v>0</v>
       </c>
-      <c r="F39" s="209"/>
-      <c r="G39" s="205" t="s">
-        <v>36</v>
-      </c>
-      <c r="H39" s="206"/>
-      <c r="I39" s="206"/>
-      <c r="J39" s="206"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="208">
+      <c r="F46" s="110"/>
+      <c r="G46" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="H46" s="104"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="104"/>
+      <c r="K46" s="105"/>
+      <c r="L46" s="109">
         <f>J4</f>
         <v>0</v>
       </c>
-      <c r="M39" s="209"/>
-    </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="207"/>
-      <c r="B40" s="94"/>
-      <c r="C40" s="94"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="210"/>
-      <c r="F40" s="211"/>
-      <c r="G40" s="207"/>
-      <c r="H40" s="94"/>
-      <c r="I40" s="94"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="95"/>
-      <c r="L40" s="210"/>
-      <c r="M40" s="211"/>
-    </row>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="71" t="s">
+      <c r="M46" s="110"/>
+    </row>
+    <row r="47" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="106"/>
+      <c r="B47" s="107"/>
+      <c r="C47" s="107"/>
+      <c r="D47" s="108"/>
+      <c r="E47" s="111"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="106"/>
+      <c r="H47" s="107"/>
+      <c r="I47" s="107"/>
+      <c r="J47" s="107"/>
+      <c r="K47" s="108"/>
+      <c r="L47" s="111"/>
+      <c r="M47" s="112"/>
+    </row>
+    <row r="48" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="87"/>
+      <c r="E48" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="72"/>
-      <c r="C41" s="72"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="74" t="s">
+      <c r="F48" s="89"/>
+      <c r="G48" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="F41" s="75"/>
-      <c r="G41" s="76" t="s">
-        <v>39</v>
-      </c>
-      <c r="H41" s="77"/>
-      <c r="I41" s="77"/>
-      <c r="J41" s="77"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="78" t="s">
-        <v>38</v>
-      </c>
-      <c r="M41" s="79"/>
+      <c r="H48" s="91"/>
+      <c r="I48" s="91"/>
+      <c r="J48" s="91"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="92" t="s">
+        <v>37</v>
+      </c>
+      <c r="M48" s="93"/>
     </row>
   </sheetData>
-  <mergeCells count="83">
+  <mergeCells count="99">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="H5:I5"/>
@@ -3600,66 +3814,82 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="J12:M12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="A19:M19"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="J21:M21"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="G35:M35"/>
-    <mergeCell ref="A36:F38"/>
-    <mergeCell ref="G36:M38"/>
-    <mergeCell ref="A39:D40"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:K40"/>
-    <mergeCell ref="L39:M40"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:M42"/>
+    <mergeCell ref="A43:F45"/>
+    <mergeCell ref="G43:M45"/>
+    <mergeCell ref="A46:D47"/>
+    <mergeCell ref="E46:F47"/>
+    <mergeCell ref="G46:K47"/>
+    <mergeCell ref="L46:M47"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3680,21 +3910,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="193"/>
+      <c r="A1" s="204" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="206"/>
       <c r="O1" s="54"/>
       <c r="P1" s="54"/>
       <c r="Q1" s="54"/>
@@ -3710,21 +3940,21 @@
       <c r="AA1" s="54"/>
     </row>
     <row r="2" spans="1:27" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="195"/>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-      <c r="I2" s="195"/>
-      <c r="J2" s="195"/>
-      <c r="K2" s="195"/>
-      <c r="L2" s="195"/>
-      <c r="M2" s="196"/>
+      <c r="B2" s="208"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="209"/>
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
       <c r="Q2" s="55"/>
@@ -3740,21 +3970,21 @@
       <c r="AA2" s="55"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="210" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="198"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="199"/>
+      <c r="B3" s="211"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="211"/>
+      <c r="H3" s="211"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="211"/>
+      <c r="M3" s="212"/>
       <c r="O3" s="42"/>
       <c r="P3" s="42"/>
       <c r="Q3" s="42"/>
@@ -3770,25 +4000,25 @@
       <c r="AA3" s="42"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="113" t="s">
+      <c r="A4" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="251">
+      <c r="J4" s="257">
         <v>46083</v>
       </c>
-      <c r="K4" s="251"/>
-      <c r="L4" s="251"/>
-      <c r="M4" s="252"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="257"/>
+      <c r="M4" s="258"/>
       <c r="O4" s="42"/>
       <c r="P4" s="42"/>
       <c r="Q4" s="42"/>
@@ -3804,25 +4034,25 @@
       <c r="AA4" s="56"/>
     </row>
     <row r="5" spans="1:27" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="188" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="201" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="201"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="189" t="s">
+      <c r="H5" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="189"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="190"/>
+      <c r="I5" s="202"/>
+      <c r="J5" s="162"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="162"/>
+      <c r="M5" s="203"/>
       <c r="O5" s="49"/>
       <c r="P5" s="49"/>
       <c r="Q5" s="57"/>
@@ -3844,13 +4074,13 @@
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="178"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="190"/>
+      <c r="J6" s="190"/>
       <c r="K6" s="14"/>
-      <c r="L6" s="178"/>
-      <c r="M6" s="179"/>
+      <c r="L6" s="190"/>
+      <c r="M6" s="236"/>
       <c r="O6" s="44"/>
       <c r="P6" s="44"/>
       <c r="Q6" s="45"/>
@@ -3887,23 +4117,23 @@
       <c r="T7" s="42"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="180" t="s">
+      <c r="A8" s="237" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
+      <c r="D8" s="253" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="244" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-      <c r="G8" s="232"/>
-      <c r="H8" s="232"/>
-      <c r="I8" s="245"/>
-      <c r="J8" s="184"/>
-      <c r="K8" s="184"/>
-      <c r="L8" s="184"/>
-      <c r="M8" s="185"/>
+      <c r="E8" s="195"/>
+      <c r="F8" s="195"/>
+      <c r="G8" s="195"/>
+      <c r="H8" s="195"/>
+      <c r="I8" s="254"/>
+      <c r="J8" s="240"/>
+      <c r="K8" s="240"/>
+      <c r="L8" s="240"/>
+      <c r="M8" s="241"/>
       <c r="O8" s="48"/>
       <c r="P8" s="48"/>
       <c r="Q8" s="48"/>
@@ -3919,21 +4149,21 @@
       <c r="AA8" s="57"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="164" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="165"/>
-      <c r="C9" s="165"/>
-      <c r="D9" s="246"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="247"/>
-      <c r="J9" s="186"/>
-      <c r="K9" s="186"/>
-      <c r="L9" s="186"/>
-      <c r="M9" s="187"/>
+      <c r="A9" s="173" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="196"/>
+      <c r="F9" s="196"/>
+      <c r="G9" s="196"/>
+      <c r="H9" s="196"/>
+      <c r="I9" s="256"/>
+      <c r="J9" s="199"/>
+      <c r="K9" s="199"/>
+      <c r="L9" s="199"/>
+      <c r="M9" s="200"/>
       <c r="O9" s="49"/>
       <c r="P9" s="49"/>
       <c r="Q9" s="49"/>
@@ -3949,25 +4179,25 @@
       <c r="AA9" s="57"/>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="161" t="s">
+      <c r="A10" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="162"/>
-      <c r="C10" s="163"/>
-      <c r="D10" s="167" t="s">
+      <c r="B10" s="171"/>
+      <c r="C10" s="172"/>
+      <c r="D10" s="176" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="168"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="168"/>
-      <c r="I10" s="169"/>
-      <c r="J10" s="168" t="s">
+      <c r="E10" s="177"/>
+      <c r="F10" s="177"/>
+      <c r="G10" s="177"/>
+      <c r="H10" s="177"/>
+      <c r="I10" s="178"/>
+      <c r="J10" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="168"/>
-      <c r="L10" s="168"/>
-      <c r="M10" s="169"/>
+      <c r="K10" s="177"/>
+      <c r="L10" s="177"/>
+      <c r="M10" s="178"/>
       <c r="O10" s="49"/>
       <c r="P10" s="49"/>
       <c r="Q10" s="49"/>
@@ -3983,19 +4213,19 @@
       <c r="AA10" s="52"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="164"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="166"/>
-      <c r="D11" s="170"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="79"/>
+      <c r="A11" s="173"/>
+      <c r="B11" s="174"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="179"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
+      <c r="L11" s="92"/>
+      <c r="M11" s="93"/>
       <c r="O11" s="49"/>
       <c r="P11" s="49"/>
       <c r="Q11" s="49"/>
@@ -4011,19 +4241,19 @@
       <c r="AA11" s="52"/>
     </row>
     <row r="12" spans="1:27" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="148"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="128"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="248"/>
-      <c r="K12" s="249"/>
-      <c r="L12" s="249"/>
-      <c r="M12" s="250"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="231"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="231"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="250"/>
+      <c r="K12" s="251"/>
+      <c r="L12" s="251"/>
+      <c r="M12" s="252"/>
       <c r="O12" s="42"/>
       <c r="P12" s="42"/>
       <c r="Q12" s="42"/>
@@ -4039,19 +4269,19 @@
       <c r="AA12" s="63"/>
     </row>
     <row r="13" spans="1:27" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="241"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="242"/>
-      <c r="L13" s="242"/>
-      <c r="M13" s="243"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="248"/>
+      <c r="K13" s="248"/>
+      <c r="L13" s="248"/>
+      <c r="M13" s="249"/>
       <c r="O13" s="42"/>
       <c r="P13" s="42"/>
       <c r="Q13" s="42"/>
@@ -4067,22 +4297,22 @@
       <c r="AA13" s="62"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="131"/>
-      <c r="B14" s="120"/>
-      <c r="C14" s="120"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="158">
+      <c r="A14" s="142"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="133"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="167">
         <f>SUM(J12:M13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="159"/>
-      <c r="L14" s="159"/>
-      <c r="M14" s="160"/>
+      <c r="K14" s="168"/>
+      <c r="L14" s="168"/>
+      <c r="M14" s="169"/>
       <c r="O14" s="42"/>
       <c r="P14" s="42"/>
       <c r="Q14" s="42"/>
@@ -4098,21 +4328,21 @@
       <c r="AA14" s="60"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="146"/>
-      <c r="C15" s="146"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="146"/>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="147"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="156"/>
+      <c r="J15" s="156"/>
+      <c r="K15" s="156"/>
+      <c r="L15" s="156"/>
+      <c r="M15" s="157"/>
       <c r="O15" s="42"/>
       <c r="P15" s="42"/>
       <c r="Q15" s="42"/>
@@ -4128,23 +4358,23 @@
       <c r="AA15" s="42"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="148" t="s">
+      <c r="A16" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="128"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="127" t="s">
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="128"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="127"/>
-      <c r="K16" s="128"/>
-      <c r="L16" s="128"/>
-      <c r="M16" s="130"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="231"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="232"/>
       <c r="O16" s="42"/>
       <c r="P16" s="42"/>
       <c r="Q16" s="42"/>
@@ -4160,21 +4390,21 @@
       <c r="AA16" s="42"/>
     </row>
     <row r="17" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="135" t="s">
+      <c r="A17" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="149"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="151"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="147"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="123"/>
+      <c r="H17" s="133"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="233"/>
+      <c r="K17" s="234"/>
+      <c r="L17" s="234"/>
+      <c r="M17" s="235"/>
       <c r="O17" s="42"/>
       <c r="P17" s="42"/>
       <c r="Q17" s="42"/>
@@ -4190,19 +4420,19 @@
       <c r="AA17" s="65"/>
     </row>
     <row r="18" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="123"/>
+      <c r="A18" s="134"/>
+      <c r="B18" s="135"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="136"/>
       <c r="O18" s="57"/>
       <c r="P18" s="57"/>
       <c r="Q18" s="57"/>
@@ -4218,25 +4448,25 @@
       <c r="AA18" s="57"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="124" t="s">
+      <c r="A19" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="125"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="127" t="s">
+      <c r="B19" s="138"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="138"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="231" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="128"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="127" t="s">
+      <c r="H19" s="83"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="231" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="128"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="130"/>
+      <c r="K19" s="83"/>
+      <c r="L19" s="83"/>
+      <c r="M19" s="232"/>
       <c r="O19" s="42"/>
       <c r="P19" s="42"/>
       <c r="Q19" s="42"/>
@@ -4252,23 +4482,23 @@
       <c r="AA19" s="42"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A20" s="131" t="s">
+      <c r="A20" s="142" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="120"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="117" t="s">
+      <c r="B20" s="133"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="120"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="132"/>
-      <c r="K20" s="133"/>
-      <c r="L20" s="133"/>
-      <c r="M20" s="134"/>
+      <c r="H20" s="133"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="144"/>
+      <c r="L20" s="144"/>
+      <c r="M20" s="145"/>
       <c r="O20" s="42"/>
       <c r="P20" s="42"/>
       <c r="Q20" s="42"/>
@@ -4284,19 +4514,19 @@
       <c r="AA20" s="64"/>
     </row>
     <row r="21" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="135"/>
-      <c r="B21" s="136"/>
-      <c r="C21" s="136"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="136"/>
-      <c r="I21" s="137"/>
-      <c r="J21" s="139"/>
-      <c r="K21" s="140"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="141"/>
+      <c r="A21" s="146"/>
+      <c r="B21" s="147"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="147"/>
+      <c r="F21" s="148"/>
+      <c r="G21" s="149"/>
+      <c r="H21" s="147"/>
+      <c r="I21" s="148"/>
+      <c r="J21" s="150"/>
+      <c r="K21" s="151"/>
+      <c r="L21" s="151"/>
+      <c r="M21" s="152"/>
       <c r="O21" s="42"/>
       <c r="P21" s="42"/>
       <c r="Q21" s="42"/>
@@ -4312,21 +4542,21 @@
       <c r="AA21" s="42"/>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A22" s="142" t="s">
+      <c r="A22" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="143"/>
-      <c r="C22" s="143"/>
-      <c r="D22" s="143"/>
-      <c r="E22" s="143"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="143"/>
-      <c r="J22" s="125"/>
-      <c r="K22" s="125"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="144"/>
+      <c r="B22" s="154"/>
+      <c r="C22" s="154"/>
+      <c r="D22" s="154"/>
+      <c r="E22" s="154"/>
+      <c r="F22" s="154"/>
+      <c r="G22" s="154"/>
+      <c r="H22" s="154"/>
+      <c r="I22" s="154"/>
+      <c r="J22" s="138"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="141"/>
       <c r="O22" s="57"/>
       <c r="P22" s="57"/>
       <c r="Q22" s="57"/>
@@ -4342,29 +4572,29 @@
       <c r="AA22" s="42"/>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="230" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="117" t="s">
+      <c r="B23" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="120"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="111" t="s">
+      <c r="C23" s="133"/>
+      <c r="D23" s="129"/>
+      <c r="E23" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111" t="s">
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111" t="s">
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="L23" s="111"/>
-      <c r="M23" s="112"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="229"/>
       <c r="O23" s="66"/>
       <c r="P23" s="42"/>
       <c r="Q23" s="42"/>
@@ -4380,35 +4610,35 @@
       <c r="AA23" s="42"/>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A24" s="119"/>
-      <c r="B24" s="110" t="s">
+      <c r="A24" s="230"/>
+      <c r="B24" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="117" t="s">
+      <c r="C24" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="118"/>
-      <c r="E24" s="110" t="s">
+      <c r="D24" s="129"/>
+      <c r="E24" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="117" t="s">
+      <c r="F24" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="118"/>
-      <c r="H24" s="110" t="s">
+      <c r="G24" s="129"/>
+      <c r="H24" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="111" t="s">
+      <c r="I24" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="111"/>
-      <c r="K24" s="110" t="s">
+      <c r="J24" s="81"/>
+      <c r="K24" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="111" t="s">
+      <c r="L24" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="M24" s="112"/>
+      <c r="M24" s="229"/>
       <c r="O24" s="66"/>
       <c r="P24" s="49"/>
       <c r="Q24" s="42"/>
@@ -4424,29 +4654,29 @@
       <c r="AA24" s="42"/>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A25" s="119"/>
-      <c r="B25" s="110"/>
+      <c r="A25" s="230"/>
+      <c r="B25" s="228"/>
       <c r="C25" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="110"/>
+      <c r="E25" s="228"/>
       <c r="F25" s="20" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="110"/>
+      <c r="H25" s="228"/>
       <c r="I25" s="20" t="s">
         <v>4</v>
       </c>
       <c r="J25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K25" s="110"/>
+      <c r="K25" s="228"/>
       <c r="L25" s="20" t="s">
         <v>4</v>
       </c>
@@ -4556,21 +4786,21 @@
       <c r="AA28" s="46"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A29" s="113" t="s">
+      <c r="A29" s="125" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="114"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="114"/>
-      <c r="E29" s="114"/>
-      <c r="F29" s="114"/>
+      <c r="B29" s="126"/>
+      <c r="C29" s="126"/>
+      <c r="D29" s="126"/>
+      <c r="E29" s="126"/>
+      <c r="F29" s="126"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="115"/>
-      <c r="L29" s="115"/>
-      <c r="M29" s="116"/>
+      <c r="J29" s="127"/>
+      <c r="K29" s="127"/>
+      <c r="L29" s="127"/>
+      <c r="M29" s="128"/>
       <c r="O29" s="42"/>
       <c r="P29" s="42"/>
       <c r="Q29" s="42"/>
@@ -4586,24 +4816,24 @@
       <c r="AA29" s="67"/>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A30" s="113" t="s">
+      <c r="A30" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="114"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
+      <c r="B30" s="126"/>
+      <c r="C30" s="126"/>
+      <c r="D30" s="126"/>
+      <c r="E30" s="126"/>
+      <c r="F30" s="126"/>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
-      <c r="J30" s="104">
+      <c r="J30" s="115">
         <f>J14</f>
         <v>0</v>
       </c>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="105"/>
+      <c r="K30" s="115"/>
+      <c r="L30" s="115"/>
+      <c r="M30" s="116"/>
       <c r="O30" s="42"/>
       <c r="P30" s="42"/>
       <c r="Q30" s="42"/>
@@ -4619,24 +4849,24 @@
       <c r="AA30" s="67"/>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A31" s="102" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="103"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="103"/>
+      <c r="A31" s="113" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="114"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="114"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="114"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
-      <c r="J31" s="104">
+      <c r="J31" s="115">
         <f>J30</f>
         <v>0</v>
       </c>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="105"/>
+      <c r="K31" s="115"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="116"/>
       <c r="O31" s="49"/>
       <c r="P31" s="49"/>
       <c r="Q31" s="49"/>
@@ -4652,21 +4882,21 @@
       <c r="AA31" s="67"/>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A32" s="102" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="103"/>
-      <c r="C32" s="103"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="103"/>
+      <c r="A32" s="113" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="114"/>
+      <c r="C32" s="114"/>
+      <c r="D32" s="114"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="114"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="105"/>
+      <c r="J32" s="115"/>
+      <c r="K32" s="115"/>
+      <c r="L32" s="115"/>
+      <c r="M32" s="116"/>
       <c r="O32" s="49"/>
       <c r="P32" s="49"/>
       <c r="Q32" s="49"/>
@@ -4682,24 +4912,24 @@
       <c r="AA32" s="67"/>
     </row>
     <row r="33" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="106" t="s">
+      <c r="A33" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="107"/>
-      <c r="C33" s="107"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-      <c r="F33" s="107"/>
-      <c r="G33" s="107"/>
-      <c r="H33" s="107"/>
-      <c r="I33" s="107"/>
-      <c r="J33" s="108">
+      <c r="B33" s="118"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="118"/>
+      <c r="G33" s="118"/>
+      <c r="H33" s="118"/>
+      <c r="I33" s="118"/>
+      <c r="J33" s="119">
         <f>SUM(J29+J30-J31+J32)</f>
         <v>0</v>
       </c>
-      <c r="K33" s="108"/>
-      <c r="L33" s="108"/>
-      <c r="M33" s="109"/>
+      <c r="K33" s="119"/>
+      <c r="L33" s="119"/>
+      <c r="M33" s="120"/>
       <c r="O33" s="57"/>
       <c r="P33" s="57"/>
       <c r="Q33" s="57"/>
@@ -4715,23 +4945,23 @@
       <c r="AA33" s="64"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A34" s="80" t="s">
+      <c r="A34" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="81"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="80" t="s">
+      <c r="B34" s="95"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="81"/>
-      <c r="L34" s="81"/>
-      <c r="M34" s="82"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="96"/>
       <c r="O34" s="57"/>
       <c r="P34" s="57"/>
       <c r="Q34" s="57"/>
@@ -4747,23 +4977,23 @@
       <c r="AA34" s="57"/>
     </row>
     <row r="35" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="238" t="s">
+      <c r="A35" s="245" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="239"/>
-      <c r="C35" s="239"/>
-      <c r="D35" s="239"/>
-      <c r="E35" s="239"/>
-      <c r="F35" s="239"/>
-      <c r="G35" s="238" t="s">
+      <c r="B35" s="246"/>
+      <c r="C35" s="246"/>
+      <c r="D35" s="246"/>
+      <c r="E35" s="246"/>
+      <c r="F35" s="246"/>
+      <c r="G35" s="245" t="s">
         <v>24</v>
       </c>
-      <c r="H35" s="239"/>
-      <c r="I35" s="239"/>
-      <c r="J35" s="239"/>
-      <c r="K35" s="239"/>
-      <c r="L35" s="239"/>
-      <c r="M35" s="240"/>
+      <c r="H35" s="246"/>
+      <c r="I35" s="246"/>
+      <c r="J35" s="246"/>
+      <c r="K35" s="246"/>
+      <c r="L35" s="246"/>
+      <c r="M35" s="247"/>
       <c r="O35" s="68"/>
       <c r="P35" s="68"/>
       <c r="Q35" s="68"/>
@@ -4779,19 +5009,19 @@
       <c r="AA35" s="68"/>
     </row>
     <row r="36" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="238"/>
-      <c r="B36" s="239"/>
-      <c r="C36" s="239"/>
-      <c r="D36" s="239"/>
-      <c r="E36" s="239"/>
-      <c r="F36" s="239"/>
-      <c r="G36" s="238"/>
-      <c r="H36" s="239"/>
-      <c r="I36" s="239"/>
-      <c r="J36" s="239"/>
-      <c r="K36" s="239"/>
-      <c r="L36" s="239"/>
-      <c r="M36" s="240"/>
+      <c r="A36" s="245"/>
+      <c r="B36" s="246"/>
+      <c r="C36" s="246"/>
+      <c r="D36" s="246"/>
+      <c r="E36" s="246"/>
+      <c r="F36" s="246"/>
+      <c r="G36" s="245"/>
+      <c r="H36" s="246"/>
+      <c r="I36" s="246"/>
+      <c r="J36" s="246"/>
+      <c r="K36" s="246"/>
+      <c r="L36" s="246"/>
+      <c r="M36" s="247"/>
       <c r="O36" s="68"/>
       <c r="P36" s="68"/>
       <c r="Q36" s="68"/>
@@ -4807,19 +5037,19 @@
       <c r="AA36" s="68"/>
     </row>
     <row r="37" spans="1:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="238"/>
-      <c r="B37" s="239"/>
-      <c r="C37" s="239"/>
-      <c r="D37" s="239"/>
-      <c r="E37" s="239"/>
-      <c r="F37" s="239"/>
-      <c r="G37" s="238"/>
-      <c r="H37" s="239"/>
-      <c r="I37" s="239"/>
-      <c r="J37" s="239"/>
-      <c r="K37" s="239"/>
-      <c r="L37" s="239"/>
-      <c r="M37" s="240"/>
+      <c r="A37" s="245"/>
+      <c r="B37" s="246"/>
+      <c r="C37" s="246"/>
+      <c r="D37" s="246"/>
+      <c r="E37" s="246"/>
+      <c r="F37" s="246"/>
+      <c r="G37" s="245"/>
+      <c r="H37" s="246"/>
+      <c r="I37" s="246"/>
+      <c r="J37" s="246"/>
+      <c r="K37" s="246"/>
+      <c r="L37" s="246"/>
+      <c r="M37" s="247"/>
       <c r="O37" s="68"/>
       <c r="P37" s="68"/>
       <c r="Q37" s="68"/>
@@ -4835,29 +5065,27 @@
       <c r="AA37" s="68"/>
     </row>
     <row r="38" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="86" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
-      <c r="D38" s="88"/>
-      <c r="E38" s="92">
+      <c r="A38" s="215"/>
+      <c r="B38" s="216"/>
+      <c r="C38" s="216"/>
+      <c r="D38" s="217"/>
+      <c r="E38" s="221">
         <f>J4</f>
         <v>46083</v>
       </c>
-      <c r="F38" s="93"/>
-      <c r="G38" s="86" t="s">
-        <v>36</v>
-      </c>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="96"/>
-      <c r="L38" s="98">
+      <c r="F38" s="105"/>
+      <c r="G38" s="215" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38" s="216"/>
+      <c r="I38" s="216"/>
+      <c r="J38" s="216"/>
+      <c r="K38" s="222"/>
+      <c r="L38" s="224">
         <f>J4</f>
         <v>46083</v>
       </c>
-      <c r="M38" s="99"/>
+      <c r="M38" s="225"/>
       <c r="O38" s="69"/>
       <c r="P38" s="69"/>
       <c r="Q38" s="69"/>
@@ -4873,19 +5101,19 @@
       <c r="AA38" s="70"/>
     </row>
     <row r="39" spans="1:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="89"/>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="95"/>
-      <c r="G39" s="89"/>
-      <c r="H39" s="90"/>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="97"/>
-      <c r="L39" s="100"/>
-      <c r="M39" s="101"/>
+      <c r="A39" s="218"/>
+      <c r="B39" s="219"/>
+      <c r="C39" s="219"/>
+      <c r="D39" s="220"/>
+      <c r="E39" s="107"/>
+      <c r="F39" s="108"/>
+      <c r="G39" s="218"/>
+      <c r="H39" s="219"/>
+      <c r="I39" s="219"/>
+      <c r="J39" s="219"/>
+      <c r="K39" s="223"/>
+      <c r="L39" s="226"/>
+      <c r="M39" s="227"/>
       <c r="O39" s="69"/>
       <c r="P39" s="69"/>
       <c r="Q39" s="69"/>
@@ -4901,27 +5129,27 @@
       <c r="AA39" s="70"/>
     </row>
     <row r="40" spans="1:27" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="237" t="s">
+      <c r="A40" s="244" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="88"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="89"/>
+      <c r="E40" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="74"/>
-      <c r="C40" s="74"/>
-      <c r="D40" s="75"/>
-      <c r="E40" s="74" t="s">
+      <c r="F40" s="89"/>
+      <c r="G40" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="F40" s="75"/>
-      <c r="G40" s="76" t="s">
-        <v>39</v>
-      </c>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
+      <c r="H40" s="91"/>
+      <c r="I40" s="91"/>
+      <c r="J40" s="91"/>
       <c r="K40" s="28"/>
-      <c r="L40" s="78" t="s">
-        <v>38</v>
-      </c>
-      <c r="M40" s="79"/>
+      <c r="L40" s="92" t="s">
+        <v>37</v>
+      </c>
+      <c r="M40" s="93"/>
       <c r="O40" s="52"/>
       <c r="P40" s="52"/>
       <c r="Q40" s="52"/>
